--- a/seed/files/ALR-2026-000123/transactions_Q3.xlsx
+++ b/seed/files/ALR-2026-000123/transactions_Q3.xlsx
@@ -5148,7 +5148,7 @@
         <v>CR</v>
       </c>
       <c r="D118" t="str">
-        <v>4,9OO.00</v>
+        <v>4.9OO.00</v>
       </c>
       <c r="E118" t="str">
         <v>USD</v>
